--- a/artfynd/A 23569-2026 artfynd.xlsx
+++ b/artfynd/A 23569-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104185676</v>
+        <v>104185665</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595512.9854067159</v>
+        <v>595495</v>
       </c>
       <c r="R2" t="n">
-        <v>7143612.292879519</v>
+        <v>7143643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104185632</v>
+        <v>104185617</v>
       </c>
       <c r="B3" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Almselberget, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595429.1942496593</v>
+        <v>595473</v>
       </c>
       <c r="R3" t="n">
-        <v>7143673.29028444</v>
+        <v>7143713</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +840,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +866,1174 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104185690</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595478</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7143711</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104185691</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595474</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7143708</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104185692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595496</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7143641</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104185661</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595470</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7143715</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104185670</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595437</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7143836</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104185608</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595521</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7143777</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104185700</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595475</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7143718</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104185703</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7143834</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104185648</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595487</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7143676</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104185673</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595491</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7143680</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104185676</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595513</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7143612</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104185632</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Almselberget, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595429</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7143673</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
